--- a/results/Int All Data -0.0/Rando_9_permute.xlsx
+++ b/results/Int All Data -0.0/Rando_9_permute.xlsx
@@ -440,1527 +440,1527 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9175365128020194</v>
+        <v>0.9008740533717995</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.917875495852867</v>
+        <v>0.905261224305806</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.917875495852867</v>
+        <v>0.9086510548142805</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9171975297511721</v>
+        <v>0.9117019022719077</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9125498106743599</v>
+        <v>0.9049222412549586</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9128822574828706</v>
+        <v>0.9072951226108907</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9128822574828706</v>
+        <v>0.9103525063108546</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9105093761269383</v>
+        <v>0.9103525063108546</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9091534439235485</v>
+        <v>0.8993098629642986</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9077975117201587</v>
+        <v>0.897269428416877</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8972628921745402</v>
+        <v>0.9027912008654886</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8843619275153263</v>
+        <v>0.9001185539127299</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8880842048323115</v>
+        <v>0.9001185539127299</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8979996844572664</v>
+        <v>0.8956529480706816</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8942708708979444</v>
+        <v>0.905548818968626</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8949619094843131</v>
+        <v>0.8998057158312298</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8996749909844933</v>
+        <v>0.8968202307969708</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8996749909844933</v>
+        <v>0.899551703930761</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8986318968626037</v>
+        <v>0.8991996483952398</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8928626487558601</v>
+        <v>0.900542508113956</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.899296790479625</v>
+        <v>0.8958424990984493</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8924909844933285</v>
+        <v>0.8952168229354489</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8924909844933285</v>
+        <v>0.8959013252794807</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8928365037865128</v>
+        <v>0.8952233591777858</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8958546700324559</v>
+        <v>0.8931763883880275</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8961871168409665</v>
+        <v>0.9195059502344032</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8979147133068879</v>
+        <v>0.92193112152903</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.895209385142445</v>
+        <v>0.9185020735665345</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8945314190407501</v>
+        <v>0.9150991705733862</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8941924359899026</v>
+        <v>0.9147863324918861</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8924844482509917</v>
+        <v>0.9225306527226831</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8935079336458709</v>
+        <v>0.9258821673278038</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8935079336458709</v>
+        <v>0.9224923368193293</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8935079336458709</v>
+        <v>0.9224923368193293</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8901115668950594</v>
+        <v>0.9187439145329968</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8887556346916696</v>
+        <v>0.9194610980887126</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8911154435629283</v>
+        <v>0.9152691128741435</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.9074389199423007</v>
+        <v>0.9132417508113956</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.9064219707897584</v>
+        <v>0.9091608817165524</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8754176433465561</v>
+        <v>0.9081700775333574</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8812130364226469</v>
+        <v>0.9085090605842048</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8920278128380815</v>
+        <v>0.9105037414352686</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8910239361702128</v>
+        <v>0.9111817075369636</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8903459700685179</v>
+        <v>0.9129681301839163</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8951048052650559</v>
+        <v>0.9125703209520375</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8832469347277316</v>
+        <v>0.9125703209520375</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8832469347277316</v>
+        <v>0.9155100522899386</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8791791381175622</v>
+        <v>0.9155035160476019</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8676341056617383</v>
+        <v>0.9006340155066714</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8598701767039307</v>
+        <v>0.9009664623151821</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8561348269022719</v>
+        <v>0.9026286963577352</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8578035971871619</v>
+        <v>0.9002427425171294</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8605154615939417</v>
+        <v>0.9036064280562568</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8767801117922827</v>
+        <v>0.907615398485395</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.8716888297872341</v>
+        <v>0.8951579967544177</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8791399206635413</v>
+        <v>0.8869505048683736</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.8778101334294988</v>
+        <v>0.8666899567255679</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.8744203029210242</v>
+        <v>0.8633197349441039</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7957174089433826</v>
+        <v>0.8633197349441039</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7983965921384781</v>
+        <v>0.830235755499459</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.8024643887486477</v>
+        <v>0.8330064460872701</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7841462315182113</v>
+        <v>0.8411355030652723</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.77499368914533</v>
+        <v>0.8424718265416516</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7671840064911648</v>
+        <v>0.8424718265416516</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7719363054453661</v>
+        <v>0.8424718265416516</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7691982960692391</v>
+        <v>0.8381434817886765</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7746220248827984</v>
+        <v>0.8346882888568338</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7637745672556797</v>
+        <v>0.8366502884962135</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7641135503065273</v>
+        <v>0.8291926613775694</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7583508384421205</v>
+        <v>0.8344081319870176</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7769949062387306</v>
+        <v>0.8402558150018031</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7519166967183555</v>
+        <v>0.8141541200865489</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.7271578615218175</v>
+        <v>0.8141541200865489</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7312321943743239</v>
+        <v>0.8008422737107825</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7315711774251713</v>
+        <v>0.7692645600432744</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.7390288045438154</v>
+        <v>0.76860620266859</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.7187355751893256</v>
+        <v>0.7682802921024161</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.7214474395961052</v>
+        <v>0.7632478362783989</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.7133118463757664</v>
+        <v>0.7676023260007212</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6868646321673278</v>
+        <v>0.7744538856833754</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6926534890010819</v>
+        <v>0.7727785791561486</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6719624504147134</v>
+        <v>0.771376893256401</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5980380003606203</v>
+        <v>0.7840434547421564</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5956651190046881</v>
+        <v>0.7918662098809953</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5949871529029931</v>
+        <v>0.7902039758384422</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5929532545979084</v>
+        <v>0.7918988910926794</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5909258925351605</v>
+        <v>0.6568912279120086</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5909258925351605</v>
+        <v>0.6467217363865849</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.605508699963938</v>
+        <v>0.590450549945907</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.6045048232960692</v>
+        <v>0.5986384331049405</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.6004304904435629</v>
+        <v>0.5993425441759826</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.6038333934367112</v>
+        <v>0.5846355481428056</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.6106653443923549</v>
+        <v>0.574674314821493</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.6232338622430581</v>
+        <v>0.5767016768842409</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.6252677605481428</v>
+        <v>0.5595311936530833</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.6249287774972954</v>
+        <v>0.5537750180310134</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.6149357645149658</v>
+        <v>0.5466302289938695</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.6132604579877389</v>
+        <v>0.5493224846736386</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.6118849170573386</v>
+        <v>0.5422234493328525</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.6252948070681572</v>
+        <v>0.5303590425531916</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5249353137396322</v>
+        <v>0.5220151911287414</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.5276602506310855</v>
+        <v>0.5330905156869816</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5225755048683736</v>
+        <v>0.5425428236566895</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5225755048683736</v>
+        <v>0.5443096375766319</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5300592769563649</v>
+        <v>0.5453396592138479</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5349684457266498</v>
+        <v>0.5503917237648756</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5305551298232961</v>
+        <v>0.5408021547060945</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5285212315182113</v>
+        <v>0.5119559141723765</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.550913721601154</v>
+        <v>0.5183573746844572</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5256067435989903</v>
+        <v>0.5190353407861522</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5129924720519293</v>
+        <v>0.5183965921384782</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5129924720519293</v>
+        <v>0.5173927154706095</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5129924720519293</v>
+        <v>0.5170471961774252</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5166755319148936</v>
+        <v>0.5448764875586007</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5245636494771007</v>
+        <v>0.551688829787234</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5276144969347277</v>
+        <v>0.5214278308690948</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5194854399567256</v>
+        <v>0.5316757573025604</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.521708889289578</v>
+        <v>0.5282989992787595</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5158808150018031</v>
+        <v>0.5282989992787595</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.512829967544176</v>
+        <v>0.5337292643346556</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.514179363505229</v>
+        <v>0.5300004507753335</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.515176703930761</v>
+        <v>0.5207050126217093</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5135144698882077</v>
+        <v>0.5145967814641182</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5125302019473494</v>
+        <v>0.5115197890371439</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5118456996033177</v>
+        <v>0.5015389469888208</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5059261179228273</v>
+        <v>0.4998309592499098</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5062716372160115</v>
+        <v>0.5005416065632888</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5107307068157231</v>
+        <v>0.5005416065632888</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5144529841327082</v>
+        <v>0.5005416065632888</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5131362693833393</v>
+        <v>0.5005416065632888</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.4977269653804544</v>
+        <v>0.5005416065632888</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.4967091146772448</v>
+        <v>0.503201181031374</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.4967091146772448</v>
+        <v>0.4932408492607284</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.4949553732419762</v>
+        <v>0.4943035521096286</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5003389830508475</v>
+        <v>0.4952682113234764</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5003389830508475</v>
+        <v>0.4959657861521817</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5</v>
+        <v>0.4923873061666065</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5</v>
+        <v>0.4835027497295348</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5</v>
+        <v>0.4859083122971511</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.4996675531914894</v>
+        <v>0.4820553101334295</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5</v>
+        <v>0.4787373782906599</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5</v>
+        <v>0.4787373782906599</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5</v>
+        <v>0.4865723043635052</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5</v>
+        <v>0.4898771637216012</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5</v>
+        <v>0.4871522268301479</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5006779661016949</v>
+        <v>0.4871522268301479</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5006779661016949</v>
+        <v>0.493429498737829</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5006779661016949</v>
+        <v>0.4894793544897224</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5003520555355211</v>
+        <v>0.4894793544897224</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5003520555355211</v>
+        <v>0.4908352866931122</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5006975748287054</v>
+        <v>0.4934360349801659</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5</v>
+        <v>0.4927711413631446</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5</v>
+        <v>0.4941270735665345</v>
       </c>
     </row>
     <row r="155">
@@ -1970,17 +1970,17 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5</v>
+        <v>0.5014082221420844</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.4993351063829787</v>
+        <v>0.499433150018031</v>
       </c>
     </row>
   </sheetData>
